--- a/output/pdf_financials_xlsx/AVCN.xlsx
+++ b/output/pdf_financials_xlsx/AVCN.xlsx
@@ -3377,28 +3377,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.515107</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.010824</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.916475</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.8472</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.808009</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.890762</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.650321</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.803884</v>
       </c>
     </row>
     <row r="93">
@@ -5996,7 +5996,11 @@
           <t>Share-based payment reserve 16,24</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -7350,7 +7354,11 @@
           <t>Share-based payment reserve 19</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -8308,7 +8316,11 @@
           <t>Share-based payment reserve 21</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -8922,7 +8934,11 @@
           <t>Share-based payment reserve 20</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -12332,7 +12348,11 @@
           <t>Share-based payment reserve (Note 16)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>1.515107</v>
       </c>

--- a/output/pdf_financials_xlsx/AVCN.xlsx
+++ b/output/pdf_financials_xlsx/AVCN.xlsx
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>34.79659</v>
+        <v>31.881195</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.549503</v>
+        <v>18.405956</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>14.400024</v>
+        <v>12.644228</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>15.038327</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>17.837103</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>16.302219</v>
       </c>
     </row>
     <row r="11">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-35.366705</v>
+        <v>-32.45131</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-16.717683</v>
+        <v>-15.574136</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-13.284683</v>
+        <v>-11.528887</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6.658692</v>
+        <v>-8.379635</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.194867</v>
+        <v>-5.642236</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>13.519859</v>
+        <v>-2.78236</v>
       </c>
     </row>
     <row r="12">
@@ -1553,28 +1553,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.069295</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.441757</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.266732</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.031004</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.19404</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.477198</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.448028</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.28063</v>
       </c>
     </row>
     <row r="35">
@@ -1615,28 +1615,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.069295</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.441757</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.25</v>
+        <v>2.516732</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.031004</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.19404</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.477198</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.448028</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.28063</v>
       </c>
     </row>
     <row r="37">
@@ -1987,28 +1987,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.9329190000000001</v>
+        <v>0.8636239999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.263756</v>
+        <v>0.821999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.239098</v>
+        <v>1.972366</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.015743</v>
+        <v>1.984739</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.804842</v>
+        <v>0.610802</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.031056</v>
+        <v>0.553858</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.959495</v>
+        <v>0.511467</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.756304</v>
+        <v>0.475674</v>
       </c>
     </row>
     <row r="49">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -21442,10 +21442,10 @@
         </is>
       </c>
       <c r="K304" s="5" t="n">
-        <v>-17.837103</v>
+        <v>17.837103</v>
       </c>
       <c r="L304" s="5" t="n">
-        <v>-16.302219</v>
+        <v>16.302219</v>
       </c>
     </row>
     <row r="305">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -24062,7 +24062,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E353" s="5" t="n">
@@ -24072,19 +24072,19 @@
         <v>-23.315721</v>
       </c>
       <c r="G353" s="5" t="n">
-        <v>-31.881195</v>
+        <v>31.881195</v>
       </c>
       <c r="H353" s="5" t="n">
-        <v>-18.405956</v>
+        <v>18.405956</v>
       </c>
       <c r="I353" s="5" t="n">
-        <v>-12.644228</v>
+        <v>12.644228</v>
       </c>
       <c r="J353" s="5" t="n">
-        <v>-15.038327</v>
+        <v>15.038327</v>
       </c>
       <c r="K353" s="5" t="n">
-        <v>-17.578454</v>
+        <v>17.578454</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">

--- a/output/pdf_financials_xlsx/AVCN.xlsx
+++ b/output/pdf_financials_xlsx/AVCN.xlsx
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-32.8617</v>
+        <v>-32.882384</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-16.77454</v>
+        <v>-16.753856</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-14.735291</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.020684</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.020684</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-32.8617</v>
+        <v>-32.882384</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-16.77454</v>
+        <v>-16.753856</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-14.735291</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-31.774709</v>
+        <v>-31.795393</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-15.880553</v>
+        <v>-15.859869</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-13.847959</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-2023.78947301377</v>
+        <v>-2025.106874896501</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-485.8063523392842</v>
+        <v>-485.1736024223395</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-342.1039057225249</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.06290298173027845</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.1234581459933761</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -4075,10 +4075,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -4097,22 +4097,22 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.05067</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.695329</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.069984</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.020065</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.016062</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.512938</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -14318,7 +14318,11 @@
           <t>Purchase of intangible assets 9</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -15294,7 +15298,11 @@
           <t>Proceeds from sale of investments 12</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -16552,7 +16560,11 @@
           <t>Purchase of intangible assets 8</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -19804,7 +19816,11 @@
           <t>Deferred tax recovery (Note 23)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -20362,7 +20378,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E285" s="5" t="n">
@@ -21918,7 +21934,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -28452,7 +28472,11 @@
           <t>Income tax recovery 24</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -30062,7 +30086,11 @@
           <t>Income tax recovery (expense) 26</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
